--- a/Project/outputs/tables/table_average_summary.xlsx
+++ b/Project/outputs/tables/table_average_summary.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:U9"/>
+  <dimension ref="A1:K9"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -446,92 +446,42 @@
       </c>
       <c r="D1" s="1" t="inlineStr">
         <is>
-          <t>VAR_MAE</t>
+          <t>VAR_MAPE</t>
         </is>
       </c>
       <c r="E1" s="1" t="inlineStr">
         <is>
-          <t>VAR_RMSE</t>
+          <t>VAR_DirAcc</t>
         </is>
       </c>
       <c r="F1" s="1" t="inlineStr">
         <is>
-          <t>VAR_MAPE</t>
+          <t>LSTM_MSE</t>
         </is>
       </c>
       <c r="G1" s="1" t="inlineStr">
         <is>
-          <t>VAR_DirAcc</t>
+          <t>LSTM_MAPE</t>
         </is>
       </c>
       <c r="H1" s="1" t="inlineStr">
         <is>
-          <t>LSTM_MSE</t>
+          <t>LSTM_DirAcc</t>
         </is>
       </c>
       <c r="I1" s="1" t="inlineStr">
         <is>
-          <t>LSTM_MAE</t>
+          <t>GRU_MSE</t>
         </is>
       </c>
       <c r="J1" s="1" t="inlineStr">
         <is>
-          <t>LSTM_RMSE</t>
+          <t>GRU_MAPE</t>
         </is>
       </c>
       <c r="K1" s="1" t="inlineStr">
         <is>
-          <t>LSTM_MAPE</t>
-        </is>
-      </c>
-      <c r="L1" s="1" t="inlineStr">
-        <is>
-          <t>LSTM_DirAcc</t>
-        </is>
-      </c>
-      <c r="M1" s="1" t="inlineStr">
-        <is>
-          <t>GRU_MSE</t>
-        </is>
-      </c>
-      <c r="N1" s="1" t="inlineStr">
-        <is>
-          <t>GRU_MAE</t>
-        </is>
-      </c>
-      <c r="O1" s="1" t="inlineStr">
-        <is>
-          <t>GRU_RMSE</t>
-        </is>
-      </c>
-      <c r="P1" s="1" t="inlineStr">
-        <is>
-          <t>GRU_MAPE</t>
-        </is>
-      </c>
-      <c r="Q1" s="1" t="inlineStr">
-        <is>
           <t>GRU_DirAcc</t>
-        </is>
-      </c>
-      <c r="R1" s="1" t="inlineStr">
-        <is>
-          <t>Best_MSE</t>
-        </is>
-      </c>
-      <c r="S1" s="1" t="inlineStr">
-        <is>
-          <t>Best_MAE</t>
-        </is>
-      </c>
-      <c r="T1" s="1" t="inlineStr">
-        <is>
-          <t>Best_RMSE</t>
-        </is>
-      </c>
-      <c r="U1" s="1" t="inlineStr">
-        <is>
-          <t>Best_MAPE</t>
         </is>
       </c>
     </row>
@@ -547,69 +497,31 @@
         </is>
       </c>
       <c r="C2" t="n">
-        <v>0.000607</v>
+        <v>0.000615</v>
       </c>
       <c r="D2" t="n">
-        <v>0.0137</v>
+        <v>7.75</v>
       </c>
       <c r="E2" t="n">
-        <v>0.0245</v>
+        <v>0.499</v>
       </c>
       <c r="F2" t="n">
-        <v>7.88</v>
+        <v>0.000378</v>
       </c>
       <c r="G2" t="n">
-        <v>0.493</v>
+        <v>6.59</v>
       </c>
       <c r="H2" t="n">
-        <v>0.000364</v>
+        <v>0.54</v>
       </c>
       <c r="I2" t="n">
-        <v>0.0105</v>
+        <v>0.000301</v>
       </c>
       <c r="J2" t="n">
-        <v>0.0189</v>
+        <v>5.67</v>
       </c>
       <c r="K2" t="n">
-        <v>5.81</v>
-      </c>
-      <c r="L2" t="n">
-        <v>0.532</v>
-      </c>
-      <c r="M2" t="n">
-        <v>0.000381</v>
-      </c>
-      <c r="N2" t="n">
-        <v>0.0111</v>
-      </c>
-      <c r="O2" t="n">
-        <v>0.0193</v>
-      </c>
-      <c r="P2" t="n">
-        <v>6.14</v>
-      </c>
-      <c r="Q2" t="n">
-        <v>0.532</v>
-      </c>
-      <c r="R2" t="inlineStr">
-        <is>
-          <t>LSTM</t>
-        </is>
-      </c>
-      <c r="S2" t="inlineStr">
-        <is>
-          <t>LSTM</t>
-        </is>
-      </c>
-      <c r="T2" t="inlineStr">
-        <is>
-          <t>LSTM</t>
-        </is>
-      </c>
-      <c r="U2" t="inlineStr">
-        <is>
-          <t>LSTM</t>
-        </is>
+        <v>0.552</v>
       </c>
     </row>
     <row r="3">
@@ -624,69 +536,31 @@
         </is>
       </c>
       <c r="C3" t="n">
-        <v>0.002259</v>
+        <v>0.00224</v>
       </c>
       <c r="D3" t="n">
-        <v>0.03</v>
+        <v>17.42</v>
       </c>
       <c r="E3" t="n">
-        <v>0.0467</v>
+        <v>0.459</v>
       </c>
       <c r="F3" t="n">
-        <v>17.49</v>
+        <v>0.001956</v>
       </c>
       <c r="G3" t="n">
-        <v>0.475</v>
+        <v>17.96</v>
       </c>
       <c r="H3" t="n">
-        <v>0.002017</v>
+        <v>0.481</v>
       </c>
       <c r="I3" t="n">
-        <v>0.029</v>
+        <v>0.001854</v>
       </c>
       <c r="J3" t="n">
-        <v>0.0441</v>
+        <v>16.4</v>
       </c>
       <c r="K3" t="n">
-        <v>16.54</v>
-      </c>
-      <c r="L3" t="n">
-        <v>0.479</v>
-      </c>
-      <c r="M3" t="n">
-        <v>0.001965</v>
-      </c>
-      <c r="N3" t="n">
-        <v>0.0286</v>
-      </c>
-      <c r="O3" t="n">
-        <v>0.0435</v>
-      </c>
-      <c r="P3" t="n">
-        <v>15.9</v>
-      </c>
-      <c r="Q3" t="n">
-        <v>0.481</v>
-      </c>
-      <c r="R3" t="inlineStr">
-        <is>
-          <t>GRU</t>
-        </is>
-      </c>
-      <c r="S3" t="inlineStr">
-        <is>
-          <t>GRU</t>
-        </is>
-      </c>
-      <c r="T3" t="inlineStr">
-        <is>
-          <t>GRU</t>
-        </is>
-      </c>
-      <c r="U3" t="inlineStr">
-        <is>
-          <t>GRU</t>
-        </is>
+        <v>0.495</v>
       </c>
     </row>
     <row r="4">
@@ -701,69 +575,31 @@
         </is>
       </c>
       <c r="C4" t="n">
-        <v>0.005551</v>
+        <v>0.005411</v>
       </c>
       <c r="D4" t="n">
-        <v>0.0464</v>
+        <v>26.39</v>
       </c>
       <c r="E4" t="n">
-        <v>0.0723</v>
+        <v>0.456</v>
       </c>
       <c r="F4" t="n">
-        <v>26.83</v>
+        <v>0.004202</v>
       </c>
       <c r="G4" t="n">
-        <v>0.469</v>
+        <v>27.18</v>
       </c>
       <c r="H4" t="n">
-        <v>0.004788</v>
+        <v>0.488</v>
       </c>
       <c r="I4" t="n">
-        <v>0.0444</v>
+        <v>0.004226</v>
       </c>
       <c r="J4" t="n">
-        <v>0.0669</v>
+        <v>24.82</v>
       </c>
       <c r="K4" t="n">
-        <v>26.07</v>
-      </c>
-      <c r="L4" t="n">
-        <v>0.486</v>
-      </c>
-      <c r="M4" t="n">
-        <v>0.004506</v>
-      </c>
-      <c r="N4" t="n">
-        <v>0.0434</v>
-      </c>
-      <c r="O4" t="n">
-        <v>0.065</v>
-      </c>
-      <c r="P4" t="n">
-        <v>25.91</v>
-      </c>
-      <c r="Q4" t="n">
-        <v>0.492</v>
-      </c>
-      <c r="R4" t="inlineStr">
-        <is>
-          <t>GRU</t>
-        </is>
-      </c>
-      <c r="S4" t="inlineStr">
-        <is>
-          <t>GRU</t>
-        </is>
-      </c>
-      <c r="T4" t="inlineStr">
-        <is>
-          <t>GRU</t>
-        </is>
-      </c>
-      <c r="U4" t="inlineStr">
-        <is>
-          <t>GRU</t>
-        </is>
+        <v>0.48</v>
       </c>
     </row>
     <row r="5">
@@ -778,69 +614,31 @@
         </is>
       </c>
       <c r="C5" t="n">
-        <v>0.014307</v>
+        <v>0.013895</v>
       </c>
       <c r="D5" t="n">
-        <v>0.0721</v>
+        <v>39.71</v>
       </c>
       <c r="E5" t="n">
-        <v>0.1159</v>
+        <v>0.482</v>
       </c>
       <c r="F5" t="n">
-        <v>40.49</v>
+        <v>0.012389</v>
       </c>
       <c r="G5" t="n">
+        <v>36.23</v>
+      </c>
+      <c r="H5" t="n">
         <v>0.491</v>
       </c>
-      <c r="H5" t="n">
-        <v>0.013613</v>
-      </c>
       <c r="I5" t="n">
-        <v>0.06950000000000001</v>
+        <v>0.013349</v>
       </c>
       <c r="J5" t="n">
-        <v>0.1121</v>
+        <v>36.41</v>
       </c>
       <c r="K5" t="n">
-        <v>39.68</v>
-      </c>
-      <c r="L5" t="n">
-        <v>0.49</v>
-      </c>
-      <c r="M5" t="n">
-        <v>0.013839</v>
-      </c>
-      <c r="N5" t="n">
-        <v>0.07240000000000001</v>
-      </c>
-      <c r="O5" t="n">
-        <v>0.1131</v>
-      </c>
-      <c r="P5" t="n">
-        <v>41.83</v>
-      </c>
-      <c r="Q5" t="n">
-        <v>0.478</v>
-      </c>
-      <c r="R5" t="inlineStr">
-        <is>
-          <t>LSTM</t>
-        </is>
-      </c>
-      <c r="S5" t="inlineStr">
-        <is>
-          <t>LSTM</t>
-        </is>
-      </c>
-      <c r="T5" t="inlineStr">
-        <is>
-          <t>LSTM</t>
-        </is>
-      </c>
-      <c r="U5" t="inlineStr">
-        <is>
-          <t>LSTM</t>
-        </is>
+        <v>0.495</v>
       </c>
     </row>
     <row r="6">
@@ -855,69 +653,31 @@
         </is>
       </c>
       <c r="C6" t="n">
-        <v>0.000556</v>
+        <v>0.000589</v>
       </c>
       <c r="D6" t="n">
-        <v>0.0118</v>
+        <v>7.32</v>
       </c>
       <c r="E6" t="n">
-        <v>0.0227</v>
+        <v>0.5</v>
       </c>
       <c r="F6" t="n">
-        <v>7.35</v>
+        <v>0.000291</v>
       </c>
       <c r="G6" t="n">
-        <v>0.515</v>
+        <v>6.65</v>
       </c>
       <c r="H6" t="n">
-        <v>0.000262</v>
+        <v>0.529</v>
       </c>
       <c r="I6" t="n">
-        <v>0.008999999999999999</v>
+        <v>0.000271</v>
       </c>
       <c r="J6" t="n">
-        <v>0.0157</v>
+        <v>5.82</v>
       </c>
       <c r="K6" t="n">
-        <v>5.95</v>
-      </c>
-      <c r="L6" t="n">
-        <v>0.534</v>
-      </c>
-      <c r="M6" t="n">
-        <v>0.00027</v>
-      </c>
-      <c r="N6" t="n">
-        <v>0.0094</v>
-      </c>
-      <c r="O6" t="n">
-        <v>0.0158</v>
-      </c>
-      <c r="P6" t="n">
-        <v>6.17</v>
-      </c>
-      <c r="Q6" t="n">
-        <v>0.543</v>
-      </c>
-      <c r="R6" t="inlineStr">
-        <is>
-          <t>LSTM</t>
-        </is>
-      </c>
-      <c r="S6" t="inlineStr">
-        <is>
-          <t>LSTM</t>
-        </is>
-      </c>
-      <c r="T6" t="inlineStr">
-        <is>
-          <t>LSTM</t>
-        </is>
-      </c>
-      <c r="U6" t="inlineStr">
-        <is>
-          <t>LSTM</t>
-        </is>
+        <v>0.523</v>
       </c>
     </row>
     <row r="7">
@@ -932,69 +692,31 @@
         </is>
       </c>
       <c r="C7" t="n">
-        <v>0.002027</v>
+        <v>0.002103</v>
       </c>
       <c r="D7" t="n">
-        <v>0.026</v>
+        <v>16.12</v>
       </c>
       <c r="E7" t="n">
-        <v>0.0436</v>
+        <v>0.492</v>
       </c>
       <c r="F7" t="n">
-        <v>16.1</v>
+        <v>0.001986</v>
       </c>
       <c r="G7" t="n">
-        <v>0.493</v>
+        <v>18.95</v>
       </c>
       <c r="H7" t="n">
-        <v>0.001672</v>
+        <v>0.511</v>
       </c>
       <c r="I7" t="n">
-        <v>0.0247</v>
+        <v>0.00196</v>
       </c>
       <c r="J7" t="n">
-        <v>0.0394</v>
+        <v>17.35</v>
       </c>
       <c r="K7" t="n">
-        <v>16.39</v>
-      </c>
-      <c r="L7" t="n">
-        <v>0.502</v>
-      </c>
-      <c r="M7" t="n">
-        <v>0.001611</v>
-      </c>
-      <c r="N7" t="n">
-        <v>0.0235</v>
-      </c>
-      <c r="O7" t="n">
-        <v>0.0386</v>
-      </c>
-      <c r="P7" t="n">
-        <v>14.92</v>
-      </c>
-      <c r="Q7" t="n">
-        <v>0.505</v>
-      </c>
-      <c r="R7" t="inlineStr">
-        <is>
-          <t>GRU</t>
-        </is>
-      </c>
-      <c r="S7" t="inlineStr">
-        <is>
-          <t>GRU</t>
-        </is>
-      </c>
-      <c r="T7" t="inlineStr">
-        <is>
-          <t>GRU</t>
-        </is>
-      </c>
-      <c r="U7" t="inlineStr">
-        <is>
-          <t>GRU</t>
-        </is>
+        <v>0.511</v>
       </c>
     </row>
     <row r="8">
@@ -1009,69 +731,31 @@
         </is>
       </c>
       <c r="C8" t="n">
-        <v>0.00391</v>
+        <v>0.004064</v>
       </c>
       <c r="D8" t="n">
-        <v>0.0387</v>
+        <v>24.55</v>
       </c>
       <c r="E8" t="n">
-        <v>0.0609</v>
+        <v>0.48</v>
       </c>
       <c r="F8" t="n">
-        <v>24.37</v>
+        <v>0.003714</v>
       </c>
       <c r="G8" t="n">
-        <v>0.485</v>
+        <v>26.28</v>
       </c>
       <c r="H8" t="n">
-        <v>0.003565</v>
+        <v>0.508</v>
       </c>
       <c r="I8" t="n">
-        <v>0.0378</v>
+        <v>0.003553</v>
       </c>
       <c r="J8" t="n">
-        <v>0.0577</v>
+        <v>24.29</v>
       </c>
       <c r="K8" t="n">
-        <v>25.06</v>
-      </c>
-      <c r="L8" t="n">
-        <v>0.497</v>
-      </c>
-      <c r="M8" t="n">
-        <v>0.003549</v>
-      </c>
-      <c r="N8" t="n">
-        <v>0.0384</v>
-      </c>
-      <c r="O8" t="n">
-        <v>0.0577</v>
-      </c>
-      <c r="P8" t="n">
-        <v>25.21</v>
-      </c>
-      <c r="Q8" t="n">
-        <v>0.496</v>
-      </c>
-      <c r="R8" t="inlineStr">
-        <is>
-          <t>GRU</t>
-        </is>
-      </c>
-      <c r="S8" t="inlineStr">
-        <is>
-          <t>LSTM</t>
-        </is>
-      </c>
-      <c r="T8" t="inlineStr">
-        <is>
-          <t>LSTM</t>
-        </is>
-      </c>
-      <c r="U8" t="inlineStr">
-        <is>
-          <t>VAR</t>
-        </is>
+        <v>0.506</v>
       </c>
     </row>
     <row r="9">
@@ -1086,69 +770,31 @@
         </is>
       </c>
       <c r="C9" t="n">
-        <v>0.007464</v>
+        <v>0.007564</v>
       </c>
       <c r="D9" t="n">
-        <v>0.0584</v>
+        <v>37.64</v>
       </c>
       <c r="E9" t="n">
-        <v>0.08450000000000001</v>
+        <v>0.507</v>
       </c>
       <c r="F9" t="n">
-        <v>37.95</v>
+        <v>0.006553</v>
       </c>
       <c r="G9" t="n">
-        <v>0.51</v>
+        <v>36.79</v>
       </c>
       <c r="H9" t="n">
-        <v>0.007164</v>
+        <v>0.522</v>
       </c>
       <c r="I9" t="n">
-        <v>0.0586</v>
+        <v>0.006674</v>
       </c>
       <c r="J9" t="n">
-        <v>0.0825</v>
+        <v>38.2</v>
       </c>
       <c r="K9" t="n">
-        <v>41.93</v>
-      </c>
-      <c r="L9" t="n">
-        <v>0.505</v>
-      </c>
-      <c r="M9" t="n">
-        <v>0.006932</v>
-      </c>
-      <c r="N9" t="n">
-        <v>0.0596</v>
-      </c>
-      <c r="O9" t="n">
-        <v>0.08110000000000001</v>
-      </c>
-      <c r="P9" t="n">
-        <v>42.45</v>
-      </c>
-      <c r="Q9" t="n">
-        <v>0.504</v>
-      </c>
-      <c r="R9" t="inlineStr">
-        <is>
-          <t>GRU</t>
-        </is>
-      </c>
-      <c r="S9" t="inlineStr">
-        <is>
-          <t>VAR</t>
-        </is>
-      </c>
-      <c r="T9" t="inlineStr">
-        <is>
-          <t>GRU</t>
-        </is>
-      </c>
-      <c r="U9" t="inlineStr">
-        <is>
-          <t>VAR</t>
-        </is>
+        <v>0.512</v>
       </c>
     </row>
   </sheetData>
